--- a/基本設計/16_業務ルールと状態遷移_基本設計書.xlsx
+++ b/基本設計/16_業務ルールと状態遷移_基本設計書.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R5ea150a788834c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R420f56529d3043c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="R8701f960cd10485f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_タスク状態遷移" sheetId="28" r:id="R21d6d95a38884d3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_業務ルール" sheetId="29" r:id="R9721e278482d41d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R8f73c0815f6948d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rad8c768263e54f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="Re9f0eb1eaed749de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_タスク状態遷移" sheetId="28" r:id="R25880a29262e4bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_業務ルール" sheetId="29" r:id="R889167d8d64544eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1178,7 +1178,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="183" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1215,10 +1215,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="189" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="E13" s="140"/>
-      <x:c r="F13" s="140"/>
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="E13" s="140" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="F13" s="140" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
       <x:c r="G13"/>
       <x:c r="H13"/>
       <x:c r="I13"/>
@@ -1233,10 +1237,14 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="189" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="E14" s="140"/>
-      <x:c r="F14" s="140"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="E14" s="140" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F14" s="140" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="G14"/>
       <x:c r="H14"/>
       <x:c r="I14"/>
@@ -1269,10 +1277,14 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="D16" s="189" t="str">
-        <x:v>Review中</x:v>
-      </x:c>
-      <x:c r="E16" s="140"/>
-      <x:c r="F16" s="140"/>
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="E16" s="140" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F16" s="140" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
       <x:c r="G16"/>
       <x:c r="H16"/>
       <x:c r="I16"/>
@@ -1302,31 +1314,73 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
+      <x:c r="B19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
+      <x:c r="B20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="B21" s="182"/>
-      <x:c r="C21" s="182"/>
-      <x:c r="D21" s="182"/>
-      <x:c r="E21" s="182"/>
-      <x:c r="F21" s="182"/>
-      <x:c r="G21" s="182"/>
-      <x:c r="H21" s="182"/>
+      <x:c r="B21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="B22"/>
@@ -1430,15 +1484,29 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="195" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="195"/>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="63"/>
-      <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="C4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="D4" s="195" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="G4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="H4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="I4"/>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -1906,6 +1974,32 @@
       </x:c>
       <x:c r="H21" s="191" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="115" customHeight="1">
+      <x:c r="A22" s="187" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B22" s="187" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="C22" s="187" t="str">
+        <x:v>ログイン試行制限の独立固定窓、5回目Lock成立・満了後再開を明確化。CHG-AUTH-20260928-01</x:v>
+      </x:c>
+      <x:c r="D22" s="187" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E22" s="187" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F22" s="187" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G22" s="187" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H22" s="187" t="str">
+        <x:v>変更指示に基づく改訂。新Baseline承認は別途記録。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1988,21 +2082,27 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="192" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="193" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
       <x:c r="E4" s="23" t="str">
         <x:v>作成日</x:v>
       </x:c>
       <x:c r="F4" s="23"/>
       <x:c r="G4" s="194" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="H4" s="24" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="I4"/>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -2871,15 +2971,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="195" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="103"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="103" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="103"/>
       <x:c r="D4" s="103"/>
       <x:c r="E4" s="195" t="str">
-        <x:v>改訂日：2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="103"/>
+        <x:v>改訂日：2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="103" t="str">
+        <x:v>改訂日：2026-09-28</x:v>
+      </x:c>
       <x:c r="G4" s="103"/>
       <x:c r="H4" s="103"/>
       <x:c r="I4" s="103"/>
@@ -4022,15 +4126,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="195" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="63"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4"/>
@@ -4130,7 +4238,7 @@
       <x:c r="K8"/>
       <x:c r="L8"/>
     </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+    <x:row r="9" ht="155" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>BR-AUTH-002</x:v>
       </x:c>
@@ -4141,22 +4249,22 @@
         <x:v>5回連続失敗で30分Lock</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>Redis Counter/locked_until</x:v>
+        <x:v>連続失敗1～4回：回数+1、AUTH-4001。第5回：count=5、locked_until=現在日時+30分、当該RequestからAUTH-4004。現在日時&lt;期限は照合せずAUTH-4004、回数・期限を保持。期限≦現在日時は次回Loginの照合前にcount=0／期限nullへReset。以後最初の失敗は1／期限null、成功は0／期限null。</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>M01</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>AUTH-4004</x:v>
+        <x:v>AUTH-4001／AUTH-4004</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
-        <x:v>成功時Clear</x:v>
-      </x:c>
-      <x:c r="I9" s="190" t="str">
-        <x:v>認証失敗。失敗回数・Lockの更新は認証規則に従う。Sessionを確立しない。</x:v>
+        <x:v>HTTP正本：10／21。DB回数・期限を正本とし、Redisは19／35に従う。停止Userの拒否を優先。</x:v>
+      </x:c>
+      <x:c r="I9" s="191" t="str">
+        <x:v>通常拒否は必要な回数／Lock更新とFAILURE履歴をCommit、Session未確立。System異常は満了解除を含む未Commit更新をRollback。</x:v>
       </x:c>
       <x:c r="J9"/>
       <x:c r="K9"/>
